--- a/presentations/heatmap_byhand/xlsx/baseline_methods/maestro_atfaa/risk_ranking_filesystemMCP_maestro.xlsx
+++ b/presentations/heatmap_byhand/xlsx/baseline_methods/maestro_atfaa/risk_ranking_filesystemMCP_maestro.xlsx
@@ -5633,12 +5633,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="72" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="20.1" customHeight="1">
@@ -5657,6 +5658,11 @@
           <t>Risk Level</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Reasoning</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="13" t="n">
@@ -5672,6 +5678,11 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>P=2 × I=3(max,critical dir+exec ft) × E=3 = 18 → Critical</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="13" t="n">
@@ -5687,6 +5698,11 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>P=2 × I=3 × E=3 = 18 → Critical (critical dir or exec filetype)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="13" t="n">
@@ -5702,6 +5718,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>P=1 × I=3 × E=3 = 9 → High (unlikely invocation, but high impact)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="9" t="n">
@@ -5717,6 +5738,11 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>P=3 × I=3 × E=3 = 27 → Critical (routine; reads critical-dir sensitive data)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="n">
@@ -5732,6 +5758,11 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>P=3 × I=3 × E=3 = 27 → Critical (routine enumeration of sensitive directories)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="n">
@@ -5747,6 +5778,11 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>P=3 × I=3 × E=3 = 27 → Critical (routine content search in critical dirs)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="9" t="n">
@@ -5762,6 +5798,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>P=1 × I=3 × E=3 = 9 → High (unlikely but critical-dir staging risk)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="11" t="n">
@@ -5775,6 +5816,11 @@
       <c r="C9" s="12" t="inlineStr">
         <is>
           <t>Critical</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>P=2 × I=3 × E=3 = 18 → Critical (plausible metadata check on critical files)</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5841,7 @@
     <col width="5.28515625" bestFit="1" customWidth="1" min="1" max="1"/>
     <col width="6.28515625" bestFit="1" customWidth="1" min="2" max="2"/>
     <col width="9.7109375" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="50.5703125" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="72" bestFit="1" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5834,7 +5880,11 @@
           <t>Critical</t>
         </is>
       </c>
-      <c r="D2" s="15" t="n"/>
+      <c r="D2" s="15" t="inlineStr">
+        <is>
+          <t>Exec filetype: raises I by +1 (cap 3); P=3(read) × I=3 × E=3 = 27 → Critical</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="13" t="n">
@@ -5850,7 +5900,11 @@
           <t>Critical</t>
         </is>
       </c>
-      <c r="D3" s="15" t="n"/>
+      <c r="D3" s="15" t="inlineStr">
+        <is>
+          <t>Exec filetype: I+1 → I=3 in high/critical dirs; P=3 × I=3 × E=3 = 27 → Critical</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="13" t="n">
@@ -5866,7 +5920,11 @@
           <t>Critical</t>
         </is>
       </c>
-      <c r="D4" s="15" t="n"/>
+      <c r="D4" s="15" t="inlineStr">
+        <is>
+          <t>Exec filetype: I+1 → I=3; read/write/search in any sensitive dir → Critical</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="9" t="n">
@@ -5882,7 +5940,11 @@
           <t>Critical</t>
         </is>
       </c>
-      <c r="D5" s="15" t="n"/>
+      <c r="D5" s="15" t="inlineStr">
+        <is>
+          <t>Exec filetype: I+1 → I=3; IP theft + supply-chain attack surface → Critical</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="n">
@@ -5898,7 +5960,11 @@
           <t>Critical</t>
         </is>
       </c>
-      <c r="D6" s="15" t="n"/>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>Exec filetype: I+1; DB schema/data exfiltration → Critical worst-case</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="n">
@@ -5914,7 +5980,11 @@
           <t>Critical</t>
         </is>
       </c>
-      <c r="D7" s="15" t="n"/>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>I unchanged (non-exec); Sensitive Docs I=3; read P=3 × I=3 × E=3 = 27 → Critical</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="n">
@@ -5930,7 +6000,11 @@
           <t>Critical</t>
         </is>
       </c>
-      <c r="D8" s="15" t="n"/>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>I unchanged; Sensitive Docs I=3; read P=3 × I=3 × E=3 = 27 → Critical</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="9" t="n">
@@ -5946,7 +6020,11 @@
           <t>Critical</t>
         </is>
       </c>
-      <c r="D9" s="15" t="n"/>
+      <c r="D9" s="15" t="inlineStr">
+        <is>
+          <t>I unchanged; Sensitive Docs I=3; read P=3 × I=3 = 27 → Critical</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="11" t="n">
@@ -5962,7 +6040,11 @@
           <t>Critical</t>
         </is>
       </c>
-      <c r="D10" s="15" t="n"/>
+      <c r="D10" s="15" t="inlineStr">
+        <is>
+          <t>I unchanged; Sensitive Docs I=3; read P=3 × I=3 = 27 → Critical</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="9" t="n">
@@ -5978,7 +6060,11 @@
           <t>Critical</t>
         </is>
       </c>
-      <c r="D11" s="15" t="n"/>
+      <c r="D11" s="15" t="inlineStr">
+        <is>
+          <t>I unchanged; Source Code I=3; read P=3 × I=3 = 27 → Critical</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="n">
@@ -5994,7 +6080,11 @@
           <t>Critical</t>
         </is>
       </c>
-      <c r="D12" s="15" t="n"/>
+      <c r="D12" s="15" t="inlineStr">
+        <is>
+          <t>I unchanged; all dirs: max I=3 (Sensitive Docs); read P=3 × I=3 = 27 → Critical</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="9" t="n">
@@ -6010,7 +6100,11 @@
           <t>Critical</t>
         </is>
       </c>
-      <c r="D13" s="15" t="n"/>
+      <c r="D13" s="15" t="inlineStr">
+        <is>
+          <t>I unchanged; Security Evidence I=3; read P=3 × I=3 = 27 → Critical</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6023,11 +6117,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5.28515625" bestFit="1" customWidth="1" min="1" max="1"/>
     <col width="14.7109375" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="72" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6046,6 +6141,11 @@
           <t>Risk Level</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Reasoning</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="13" t="n">
@@ -6061,6 +6161,11 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>I=3 (PII/contracts/financials); write P=2 → R=18 Critical; read P=3 → R=27 Critical</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="13" t="n">
@@ -6076,6 +6181,11 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>I=3 (audit integrity); read P=3 → R=27 Critical; write P=2 → R=18 Critical</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="13" t="n">
@@ -6091,6 +6201,11 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>I=3 (IP/supply-chain); exec filetypes raise I to 3; read P=3 → R=27 Critical</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="9" t="n">
@@ -6106,6 +6221,11 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>I=2 (research data); exec ft raises I to 3; read P=3 × I=3 × E=3 = 27 → Critical</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="n">
@@ -6121,6 +6241,11 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>I=2; exec ft raises I to 3; read P=3 × I=3 = 27 → Critical worst-case</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="n">
@@ -6136,6 +6261,11 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>I=2; exec ft raises I to 3; read P=3 × I=3 = 27 → Critical worst-case</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="n">
@@ -6151,6 +6281,11 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>I=2; exec ft raises I to 3; read P=3 × I=3 = 27 → Critical worst-case</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="9" t="n">
@@ -6166,7 +6301,13 @@
           <t>Critical</t>
         </is>
       </c>
-    </row>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>I=1; exec ft raises I to min(1+1,3)=2; write P=2 × I=2 × E=3 = 12 → High</t>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
     <row r="11">
       <c r="B11" t="inlineStr">
         <is>
